--- a/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,55; 50,66</t>
+          <t>32,0; 50,88</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,05; 45,05</t>
+          <t>24,9; 45,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 2,36</t>
+          <t>-24,72; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,49; 47,36</t>
+          <t>30,02; 47,91</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,63; 38,56</t>
+          <t>18,17; 38,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,03; 9,05</t>
+          <t>-17,05; 8,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,32; 46,0</t>
+          <t>33,52; 46,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,62; 38,17</t>
+          <t>24,38; 38,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 2,45</t>
+          <t>-16,91; 1,63</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,88; 107,94</t>
+          <t>49,75; 108,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,52; 95,7</t>
+          <t>39,07; 95,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 5,18</t>
+          <t>-39,82; 2,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,43; 94,13</t>
+          <t>44,88; 97,13</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,48; 75,06</t>
+          <t>28,31; 76,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 16,35</t>
+          <t>-27,22; 15,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,26; 89,25</t>
+          <t>53,34; 91,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,65; 72,37</t>
+          <t>38,78; 75,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,53; 4,53</t>
+          <t>-27,81; 1,98</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,58; 57,68</t>
+          <t>43,37; 57,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,19; 49,5</t>
+          <t>34,84; 50,11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 6,28</t>
+          <t>-9,86; 7,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,07; 64,25</t>
+          <t>51,97; 65,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,45; 53,24</t>
+          <t>38,15; 52,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 16,26</t>
+          <t>-0,33; 15,94</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,23; 59,3</t>
+          <t>49,5; 59,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,02; 49,38</t>
+          <t>39,06; 50,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 8,61</t>
+          <t>-3,0; 8,56</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>105,18; 180,72</t>
+          <t>101,84; 182,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80,75; 153,56</t>
+          <t>85,1; 159,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 18,69</t>
+          <t>-24,7; 21,98</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129,31; 221,22</t>
+          <t>130,8; 224,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,13; 181,35</t>
+          <t>97,8; 178,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 53,77</t>
+          <t>-1,16; 55,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>125,33; 185,07</t>
+          <t>124,99; 188,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>99,78; 153,38</t>
+          <t>100,67; 157,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 26,39</t>
+          <t>-7,81; 26,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,22; 56,04</t>
+          <t>34,89; 57,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,35; 41,37</t>
+          <t>21,03; 41,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 12,97</t>
+          <t>-7,34; 13,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40,56; 59,15</t>
+          <t>39,9; 58,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27,35; 47,26</t>
+          <t>28,94; 48,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 10,82</t>
+          <t>-7,87; 10,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,35; 55,61</t>
+          <t>40,38; 55,16</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,13; 41,8</t>
+          <t>27,34; 42,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 9,33</t>
+          <t>-4,31; 9,53</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90,13; 240,1</t>
+          <t>91,56; 247,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,36; 175,92</t>
+          <t>57,55; 177,55</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,55; 53,94</t>
+          <t>-20,93; 57,25</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>114,24; 266,34</t>
+          <t>120,31; 266,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>78,65; 215,93</t>
+          <t>87,8; 217,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-22,83; 50,53</t>
+          <t>-23,75; 46,56</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>120,12; 226,56</t>
+          <t>119,12; 234,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>80,78; 170,34</t>
+          <t>83,05; 175,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,88; 37,3</t>
+          <t>-13,05; 40,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>46,2; 62,66</t>
+          <t>45,33; 62,28</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,45; 37,35</t>
+          <t>19,4; 36,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,79; 17,94</t>
+          <t>1,83; 17,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,47; 62,08</t>
+          <t>46,08; 61,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,27; 42,24</t>
+          <t>23,85; 41,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,92; 28,72</t>
+          <t>13,01; 28,78</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,71; 59,45</t>
+          <t>47,61; 59,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,3; 36,72</t>
+          <t>24,27; 36,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,77; 21,89</t>
+          <t>9,6; 21,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>267,67; 647,1</t>
+          <t>259,67; 654,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>112,14; 376,35</t>
+          <t>116,98; 359,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10,35; 165,92</t>
+          <t>13,16; 176,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>338,17; 891,14</t>
+          <t>323,21; 883,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>193,07; 565,21</t>
+          <t>181,36; 557,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>93,63; 378,19</t>
+          <t>93,2; 368,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>341,36; 640,54</t>
+          <t>329,96; 641,4</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>173,24; 392,22</t>
+          <t>174,18; 383,84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>71,26; 219,06</t>
+          <t>72,07; 221,21</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,51; 55,17</t>
+          <t>46,57; 55,47</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,47; 40,94</t>
+          <t>31,62; 41,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 4,0</t>
+          <t>-6,9; 4,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49,08; 57,45</t>
+          <t>48,94; 57,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,91; 43,83</t>
+          <t>34,55; 44,17</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 9,47</t>
+          <t>-0,74; 8,84</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,15; 55,11</t>
+          <t>49,2; 55,04</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,83; 41,33</t>
+          <t>34,7; 41,13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 5,52</t>
+          <t>-1,92; 5,43</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>134,61; 191,51</t>
+          <t>132,73; 193,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>91,9; 141,24</t>
+          <t>91,34; 144,81</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-18,6; 13,64</t>
+          <t>-20,11; 14,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147,63; 211,23</t>
+          <t>147,56; 210,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>106,73; 158,7</t>
+          <t>105,35; 160,46</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 33,79</t>
+          <t>-1,94; 31,66</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>150,17; 191,79</t>
+          <t>148,36; 189,84</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>106,02; 143,69</t>
+          <t>104,85; 141,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 18,81</t>
+          <t>-5,99; 18,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,0; 50,88</t>
+          <t>33,2; 51,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,9; 45,25</t>
+          <t>25,15; 45,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,72; 1,35</t>
+          <t>-26,25; 1,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>30,02; 47,91</t>
+          <t>29,46; 46,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,17; 38,34</t>
+          <t>17,63; 36,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 8,36</t>
+          <t>-16,98; 8,46</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,52; 46,42</t>
+          <t>34,13; 46,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,38; 38,79</t>
+          <t>24,16; 38,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,91; 1,63</t>
+          <t>-16,95; 1,33</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,75; 108,45</t>
+          <t>52,17; 113,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,07; 95,53</t>
+          <t>39,84; 99,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-39,82; 2,88</t>
+          <t>-42,66; 2,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,88; 97,13</t>
+          <t>43,85; 91,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,31; 76,54</t>
+          <t>26,69; 72,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,22; 15,53</t>
+          <t>-26,86; 16,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,34; 91,88</t>
+          <t>54,22; 91,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,78; 75,93</t>
+          <t>38,33; 74,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-27,81; 1,98</t>
+          <t>-27,89; 2,18</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,37; 57,44</t>
+          <t>43,7; 57,05</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34,84; 50,11</t>
+          <t>35,07; 50,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,86; 7,13</t>
+          <t>-10,5; 6,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,97; 65,1</t>
+          <t>51,59; 64,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,15; 52,19</t>
+          <t>38,6; 52,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 15,94</t>
+          <t>-1,0; 15,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,5; 59,59</t>
+          <t>49,85; 59,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,06; 50,04</t>
+          <t>39,13; 49,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 8,56</t>
+          <t>-3,4; 9,19</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>101,84; 182,52</t>
+          <t>104,86; 180,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>85,1; 159,74</t>
+          <t>84,39; 159,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-24,7; 21,98</t>
+          <t>-25,38; 19,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130,8; 224,76</t>
+          <t>131,29; 220,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,8; 178,75</t>
+          <t>96,52; 177,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 55,1</t>
+          <t>-2,98; 49,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>124,99; 188,26</t>
+          <t>127,9; 186,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>100,67; 157,09</t>
+          <t>99,78; 154,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 26,61</t>
+          <t>-8,59; 27,98</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,89; 57,14</t>
+          <t>35,06; 56,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,03; 41,8</t>
+          <t>21,34; 41,8</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,34; 13,84</t>
+          <t>-7,24; 13,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,9; 58,58</t>
+          <t>39,67; 59,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,94; 48,07</t>
+          <t>28,94; 48,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 10,36</t>
+          <t>-8,13; 10,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,38; 55,16</t>
+          <t>40,89; 54,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,34; 42,11</t>
+          <t>27,97; 42,13</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 9,53</t>
+          <t>-4,39; 9,8</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>91,56; 247,92</t>
+          <t>93,13; 233,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>57,55; 177,55</t>
+          <t>55,86; 175,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,93; 57,25</t>
+          <t>-19,48; 56,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>120,31; 266,65</t>
+          <t>114,67; 274,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>87,8; 217,93</t>
+          <t>83,9; 225,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-23,75; 46,56</t>
+          <t>-24,59; 48,6</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>119,12; 234,06</t>
+          <t>122,69; 230,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83,05; 175,9</t>
+          <t>84,72; 173,46</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,05; 40,1</t>
+          <t>-13,11; 41,77</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>45,33; 62,28</t>
+          <t>44,9; 61,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,4; 36,77</t>
+          <t>18,52; 36,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,83; 17,76</t>
+          <t>2,2; 18,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,08; 61,82</t>
+          <t>46,1; 61,11</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,85; 41,76</t>
+          <t>25,6; 42,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,01; 28,78</t>
+          <t>12,75; 29,59</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,61; 59,51</t>
+          <t>47,81; 58,98</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,27; 36,34</t>
+          <t>24,5; 36,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,6; 21,3</t>
+          <t>9,07; 21,8</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>259,67; 654,36</t>
+          <t>264,93; 633,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>116,98; 359,59</t>
+          <t>110,71; 357,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13,16; 176,43</t>
+          <t>11,72; 187,14</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>323,21; 883,07</t>
+          <t>317,17; 855,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>181,36; 557,42</t>
+          <t>183,46; 581,08</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>93,2; 368,7</t>
+          <t>91,75; 390,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>329,96; 641,4</t>
+          <t>334,05; 629,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>174,18; 383,84</t>
+          <t>175,88; 376,05</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>72,07; 221,21</t>
+          <t>66,47; 229,61</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,57; 55,47</t>
+          <t>46,41; 55,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,62; 41,35</t>
+          <t>31,65; 41,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,9; 4,15</t>
+          <t>-6,32; 4,04</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>48,94; 57,36</t>
+          <t>49,61; 57,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,55; 44,17</t>
+          <t>34,79; 43,89</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 8,84</t>
+          <t>-0,65; 8,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,2; 55,04</t>
+          <t>49,4; 55,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,7; 41,13</t>
+          <t>34,92; 41,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 5,43</t>
+          <t>-1,66; 5,66</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>132,73; 193,69</t>
+          <t>134,55; 195,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>91,34; 144,81</t>
+          <t>89,73; 141,25</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,11; 14,21</t>
+          <t>-18,89; 13,79</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>147,56; 210,6</t>
+          <t>148,1; 207,39</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>105,35; 160,46</t>
+          <t>107,23; 158,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 31,66</t>
+          <t>-2,1; 31,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>148,36; 189,84</t>
+          <t>149,52; 190,04</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>104,85; 141,51</t>
+          <t>106,43; 144,43</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 18,29</t>
+          <t>-5,06; 19,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P2B_R-Edad-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>38,37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28,11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,73</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>41,57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>34,87</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-11,44</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38,37</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>28,11</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-4,48</t>
+          <t>-13,23</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,88</t>
+          <t>-9,16</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33,2; 51,56</t>
+          <t>29,49; 47,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25,15; 45,98</t>
+          <t>18,63; 38,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,25; 1,43</t>
+          <t>-17,05; 9,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29,46; 46,45</t>
+          <t>32,55; 50,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,63; 36,83</t>
+          <t>25,05; 45,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,98; 8,46</t>
+          <t>-25,84; 0,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,13; 46,77</t>
+          <t>33,32; 46,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24,16; 38,47</t>
+          <t>24,62; 38,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 1,33</t>
+          <t>-17,62; 0,82</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>65,59%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48,05%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-8,08%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>74,41%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>62,42%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-20,47%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>65,59%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>48,05%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-7,65%</t>
+          <t>-23,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-13,76%</t>
+          <t>-15,99%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,17; 113,42</t>
+          <t>44,43; 94,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,84; 99,22</t>
+          <t>28,48; 75,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-42,66; 2,73</t>
+          <t>-27,21; 16,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>43,85; 91,43</t>
+          <t>49,88; 107,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,69; 72,29</t>
+          <t>39,52; 95,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,86; 16,8</t>
+          <t>-42,12; -0,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,22; 91,91</t>
+          <t>52,26; 89,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>38,33; 74,19</t>
+          <t>38,65; 72,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 2,18</t>
+          <t>-29,03; 1,69</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>57,91</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>45,84</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,73</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>50,77</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>42,81</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-1,92</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>57,91</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>45,84</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>7,11</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>3,83</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>43,7; 57,05</t>
+          <t>51,07; 64,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>35,07; 50,24</t>
+          <t>38,45; 53,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 6,31</t>
+          <t>-0,5; 16,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>51,59; 64,34</t>
+          <t>43,58; 57,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>38,6; 52,74</t>
+          <t>34,19; 49,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 15,48</t>
+          <t>-9,02; 7,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>49,85; 59,42</t>
+          <t>49,23; 59,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39,13; 49,51</t>
+          <t>39,02; 49,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 9,19</t>
+          <t>-2,39; 9,41</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>168,3%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>133,22%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>22,47%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>137,66%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>116,07%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-5,21%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>168,3%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>133,22%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>-0,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>104,86; 180,71</t>
+          <t>129,31; 221,22</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>84,39; 159,15</t>
+          <t>97,13; 181,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-25,38; 19,12</t>
+          <t>-0,67; 54,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>131,29; 220,39</t>
+          <t>105,18; 180,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,52; 177,26</t>
+          <t>80,75; 153,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,98; 49,98</t>
+          <t>-22,43; 24,13</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>127,9; 186,45</t>
+          <t>125,33; 185,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>99,78; 154,42</t>
+          <t>99,78; 153,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 27,98</t>
+          <t>-6,28; 29,07</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>49,85</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>38,31</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,92</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>46,27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>31,75</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>3,52</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>49,85</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>38,31</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>5,5</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>4,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,06; 56,73</t>
+          <t>40,56; 59,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,34; 41,8</t>
+          <t>27,35; 47,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 13,42</t>
+          <t>-5,73; 13,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,67; 59,23</t>
+          <t>34,22; 56,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>28,94; 48,27</t>
+          <t>20,35; 41,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 10,15</t>
+          <t>-5,0; 15,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>40,89; 54,81</t>
+          <t>40,35; 55,61</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>27,97; 42,13</t>
+          <t>27,13; 41,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 9,8</t>
+          <t>-2,95; 11,15</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>180,86%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>138,99%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14,23%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>153,1%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>105,08%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>11,66%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>180,86%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>138,99%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>93,13; 233,95</t>
+          <t>114,24; 266,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>55,86; 175,01</t>
+          <t>78,65; 215,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-19,48; 56,77</t>
+          <t>-17,24; 60,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>114,67; 274,62</t>
+          <t>90,13; 240,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83,9; 225,6</t>
+          <t>55,36; 175,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-24,59; 48,6</t>
+          <t>-14,0; 60,77</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>122,69; 230,34</t>
+          <t>120,12; 226,56</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84,72; 173,46</t>
+          <t>80,78; 170,34</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,11; 41,77</t>
+          <t>-8,8; 45,14</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>54,08</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33,53</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21,31</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>54,05</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>27,72</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>10,58</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>54,08</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>33,53</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,76</t>
+          <t>11,9</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>15,31</t>
+          <t>16,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>44,9; 61,68</t>
+          <t>46,47; 62,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>18,52; 36,07</t>
+          <t>25,27; 42,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,2; 18,97</t>
+          <t>14,17; 29,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>46,1; 61,11</t>
+          <t>46,2; 62,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,6; 42,64</t>
+          <t>18,45; 37,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,75; 29,59</t>
+          <t>5,04; 18,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,81; 58,98</t>
+          <t>47,71; 59,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>24,5; 36,36</t>
+          <t>24,3; 36,72</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,07; 21,8</t>
+          <t>12,0; 22,28</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>538,27%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>333,68%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>212,13%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>408,03%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>209,27%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>79,9%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>538,27%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>333,68%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>196,68%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>131,31%</t>
+          <t>144,03%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>264,93; 633,6</t>
+          <t>338,17; 891,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>110,71; 357,07</t>
+          <t>193,07; 565,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,72; 187,14</t>
+          <t>107,3; 393,35</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>317,17; 855,15</t>
+          <t>267,67; 647,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>183,46; 581,08</t>
+          <t>112,14; 376,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,75; 390,66</t>
+          <t>29,14; 175,22</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>334,05; 629,0</t>
+          <t>341,36; 640,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>175,88; 376,05</t>
+          <t>173,24; 392,22</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>66,47; 229,61</t>
+          <t>87,12; 232,76</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>53,3</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>39,45</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>5,12</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>50,96</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>36,4</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,76</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>53,3</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>39,45</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,11</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>1,81</t>
+          <t>2,95</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>46,41; 55,89</t>
+          <t>49,08; 57,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31,65; 41,27</t>
+          <t>34,91; 43,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,04</t>
+          <t>0,54; 10,19</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>49,61; 57,63</t>
+          <t>46,51; 55,17</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>34,79; 43,89</t>
+          <t>31,47; 40,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,65; 8,85</t>
+          <t>-3,97; 5,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>49,4; 55,03</t>
+          <t>49,15; 55,11</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>34,92; 41,77</t>
+          <t>34,83; 41,33</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,66</t>
+          <t>-0,38; 6,52</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>176,04%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>130,28%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>16,92%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>161,23%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>115,17%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-2,41%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>176,04%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>130,28%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>134,55; 195,41</t>
+          <t>147,63; 211,23</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>89,73; 141,25</t>
+          <t>106,73; 158,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 13,79</t>
+          <t>1,64; 37,37</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>148,1; 207,39</t>
+          <t>134,61; 191,51</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>107,23; 158,95</t>
+          <t>91,9; 141,24</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 31,79</t>
+          <t>-11,49; 17,22</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>149,52; 190,04</t>
+          <t>150,17; 191,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>106,43; 144,43</t>
+          <t>106,02; 143,69</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-5,06; 19,6</t>
+          <t>-1,18; 22,1</t>
         </is>
       </c>
     </row>
